--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4583</f>
+              <f>'Chart'!$D$2:$D$4584</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4583</f>
+              <f>'Chart'!$B$2:$B$4584</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4583</f>
+              <f>'Chart'!$D$2:$D$4584</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4583</f>
+              <f>'Chart'!$C$2:$C$4584</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -687,7 +687,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 03 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 04 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4583"/>
+  <dimension ref="A1:D4584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37604,6 +37604,9 @@
       <c r="A4582" s="3" t="n">
         <v>46297</v>
       </c>
+      <c r="B4582" t="n">
+        <v>9.619999999999999</v>
+      </c>
       <c r="C4582" t="n">
         <v>11.3</v>
       </c>
@@ -37614,6 +37617,14 @@
       </c>
       <c r="C4583" t="n">
         <v>11.1</v>
+      </c>
+    </row>
+    <row r="4584">
+      <c r="A4584" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C4584" t="n">
+        <v>11.8</v>
       </c>
     </row>
   </sheetData>
@@ -37628,7 +37639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4583"/>
+  <dimension ref="A1:D4584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74543,6 +74554,12 @@
       <c r="A4582" s="4" t="n">
         <v>46297</v>
       </c>
+      <c r="B4582" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="C4582" t="n">
+        <v>9.6678</v>
+      </c>
       <c r="D4582" t="n">
         <v>11.3</v>
       </c>
@@ -74553,6 +74570,14 @@
       </c>
       <c r="D4583" t="n">
         <v>11.1</v>
+      </c>
+    </row>
+    <row r="4584">
+      <c r="A4584" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="D4584" t="n">
+        <v>11.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4584</f>
+              <f>'Chart'!$D$2:$D$4585</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4584</f>
+              <f>'Chart'!$B$2:$B$4585</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4584</f>
+              <f>'Chart'!$D$2:$D$4585</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4584</f>
+              <f>'Chart'!$C$2:$C$4585</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -687,7 +687,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 04 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 05 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4584"/>
+  <dimension ref="A1:D4585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37615,6 +37615,9 @@
       <c r="A4583" s="3" t="n">
         <v>46298</v>
       </c>
+      <c r="B4583" t="n">
+        <v>9.960000000000001</v>
+      </c>
       <c r="C4583" t="n">
         <v>11.1</v>
       </c>
@@ -37625,6 +37628,14 @@
       </c>
       <c r="C4584" t="n">
         <v>11.8</v>
+      </c>
+    </row>
+    <row r="4585">
+      <c r="A4585" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C4585" t="n">
+        <v>11.9</v>
       </c>
     </row>
   </sheetData>
@@ -37639,7 +37650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4584"/>
+  <dimension ref="A1:D4585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74568,6 +74579,12 @@
       <c r="A4583" s="4" t="n">
         <v>46298</v>
       </c>
+      <c r="B4583" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="C4583" t="n">
+        <v>10.0967</v>
+      </c>
       <c r="D4583" t="n">
         <v>11.1</v>
       </c>
@@ -74578,6 +74595,14 @@
       </c>
       <c r="D4584" t="n">
         <v>11.8</v>
+      </c>
+    </row>
+    <row r="4585">
+      <c r="A4585" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D4585" t="n">
+        <v>11.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4585</f>
+              <f>'Chart'!$D$2:$D$4586</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4585</f>
+              <f>'Chart'!$B$2:$B$4586</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4585</f>
+              <f>'Chart'!$D$2:$D$4586</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4585</f>
+              <f>'Chart'!$C$2:$C$4586</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -687,7 +687,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 05 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 06 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4585"/>
+  <dimension ref="A1:D4586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37626,6 +37626,9 @@
       <c r="A4584" s="3" t="n">
         <v>46299</v>
       </c>
+      <c r="B4584" t="n">
+        <v>10.5</v>
+      </c>
       <c r="C4584" t="n">
         <v>11.8</v>
       </c>
@@ -37636,6 +37639,14 @@
       </c>
       <c r="C4585" t="n">
         <v>11.9</v>
+      </c>
+    </row>
+    <row r="4586">
+      <c r="A4586" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C4586" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -37650,7 +37661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4585"/>
+  <dimension ref="A1:D4586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74593,6 +74604,12 @@
       <c r="A4584" s="4" t="n">
         <v>46299</v>
       </c>
+      <c r="B4584" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C4584" t="n">
+        <v>10.4986</v>
+      </c>
       <c r="D4584" t="n">
         <v>11.8</v>
       </c>
@@ -74603,6 +74620,14 @@
       </c>
       <c r="D4585" t="n">
         <v>11.9</v>
+      </c>
+    </row>
+    <row r="4586">
+      <c r="A4586" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="D4586" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4586</f>
+              <f>'Chart'!$D$2:$D$4587</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4586</f>
+              <f>'Chart'!$B$2:$B$4587</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4586</f>
+              <f>'Chart'!$D$2:$D$4587</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4586</f>
+              <f>'Chart'!$C$2:$C$4587</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -687,7 +687,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 06 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 07 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4586"/>
+  <dimension ref="A1:D4587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37637,6 +37637,9 @@
       <c r="A4585" s="3" t="n">
         <v>46300</v>
       </c>
+      <c r="B4585" t="n">
+        <v>10.3989</v>
+      </c>
       <c r="C4585" t="n">
         <v>11.9</v>
       </c>
@@ -37647,6 +37650,14 @@
       </c>
       <c r="C4586" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="4587">
+      <c r="A4587" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C4587" t="n">
+        <v>12.2</v>
       </c>
     </row>
   </sheetData>
@@ -37661,7 +37672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4586"/>
+  <dimension ref="A1:D4587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74618,6 +74629,12 @@
       <c r="A4585" s="4" t="n">
         <v>46300</v>
       </c>
+      <c r="B4585" t="n">
+        <v>10.3989</v>
+      </c>
+      <c r="C4585" t="n">
+        <v>10.404</v>
+      </c>
       <c r="D4585" t="n">
         <v>11.9</v>
       </c>
@@ -74628,6 +74645,14 @@
       </c>
       <c r="D4586" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="4587">
+      <c r="A4587" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="D4587" t="n">
+        <v>12.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4587</f>
+              <f>'Chart'!$D$2:$D$4588</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4587</f>
+              <f>'Chart'!$B$2:$B$4588</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4587</f>
+              <f>'Chart'!$D$2:$D$4588</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4587</f>
+              <f>'Chart'!$C$2:$C$4588</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -687,7 +687,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 07 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 08 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4587"/>
+  <dimension ref="A1:D4588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37648,6 +37648,9 @@
       <c r="A4586" s="3" t="n">
         <v>46301</v>
       </c>
+      <c r="B4586" t="n">
+        <v>10.62</v>
+      </c>
       <c r="C4586" t="n">
         <v>12</v>
       </c>
@@ -37658,6 +37661,14 @@
       </c>
       <c r="C4587" t="n">
         <v>12.2</v>
+      </c>
+    </row>
+    <row r="4588">
+      <c r="A4588" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C4588" t="n">
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>
@@ -37672,7 +37683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4587"/>
+  <dimension ref="A1:D4588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74643,6 +74654,12 @@
       <c r="A4586" s="4" t="n">
         <v>46301</v>
       </c>
+      <c r="B4586" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="C4586" t="n">
+        <v>10.6336</v>
+      </c>
       <c r="D4586" t="n">
         <v>12</v>
       </c>
@@ -74653,6 +74670,14 @@
       </c>
       <c r="D4587" t="n">
         <v>12.2</v>
+      </c>
+    </row>
+    <row r="4588">
+      <c r="A4588" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="D4588" t="n">
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Australia gas hub prices: Victoria DWGM and Wallumbilla (AEMO) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -191,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4588</f>
+              <f>'Chart'!$D$2:$D$4589</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4588</f>
+              <f>'Chart'!$B$2:$B$4589</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4588</f>
+              <f>'Chart'!$D$2:$D$4589</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4588</f>
+              <f>'Chart'!$C$2:$C$4589</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -687,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 08 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 09 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -724,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4588"/>
+  <dimension ref="A1:D4589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37659,6 +37660,9 @@
       <c r="A4587" s="3" t="n">
         <v>46302</v>
       </c>
+      <c r="B4587" t="n">
+        <v>10.6502</v>
+      </c>
       <c r="C4587" t="n">
         <v>12.2</v>
       </c>
@@ -37668,6 +37672,14 @@
         <v>46303</v>
       </c>
       <c r="C4588" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4589">
+      <c r="A4589" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C4589" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -37683,7 +37695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4588"/>
+  <dimension ref="A1:D4589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74668,6 +74680,12 @@
       <c r="A4587" s="4" t="n">
         <v>46302</v>
       </c>
+      <c r="B4587" t="n">
+        <v>10.6502</v>
+      </c>
+      <c r="C4587" t="n">
+        <v>9.6183</v>
+      </c>
       <c r="D4587" t="n">
         <v>12.2</v>
       </c>
@@ -74677,6 +74695,14 @@
         <v>46303</v>
       </c>
       <c r="D4588" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4589">
+      <c r="A4589" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="D4589" t="n">
         <v>12.5</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4589</f>
+              <f>'Chart'!$D$2:$D$4590</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4589</f>
+              <f>'Chart'!$B$2:$B$4590</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4589</f>
+              <f>'Chart'!$D$2:$D$4590</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4589</f>
+              <f>'Chart'!$C$2:$C$4590</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 09 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 10 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4589"/>
+  <dimension ref="A1:D4590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37671,6 +37671,9 @@
       <c r="A4588" s="3" t="n">
         <v>46303</v>
       </c>
+      <c r="B4588" t="n">
+        <v>10.6545</v>
+      </c>
       <c r="C4588" t="n">
         <v>12.5</v>
       </c>
@@ -37680,6 +37683,14 @@
         <v>46304</v>
       </c>
       <c r="C4589" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4590">
+      <c r="A4590" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C4590" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -37695,7 +37706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4589"/>
+  <dimension ref="A1:D4590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74694,6 +74705,12 @@
       <c r="A4588" s="4" t="n">
         <v>46303</v>
       </c>
+      <c r="B4588" t="n">
+        <v>10.6545</v>
+      </c>
+      <c r="C4588" t="n">
+        <v>10.6513</v>
+      </c>
       <c r="D4588" t="n">
         <v>12.5</v>
       </c>
@@ -74703,6 +74720,14 @@
         <v>46304</v>
       </c>
       <c r="D4589" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4590">
+      <c r="A4590" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="D4590" t="n">
         <v>12.5</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4590</f>
+              <f>'Chart'!$D$2:$D$4591</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4590</f>
+              <f>'Chart'!$B$2:$B$4591</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4590</f>
+              <f>'Chart'!$D$2:$D$4591</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4590</f>
+              <f>'Chart'!$C$2:$C$4591</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 10 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 11 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4590"/>
+  <dimension ref="A1:D4591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37682,6 +37682,9 @@
       <c r="A4589" s="3" t="n">
         <v>46304</v>
       </c>
+      <c r="B4589" t="n">
+        <v>10.1</v>
+      </c>
       <c r="C4589" t="n">
         <v>12.5</v>
       </c>
@@ -37692,6 +37695,14 @@
       </c>
       <c r="C4590" t="n">
         <v>12.5</v>
+      </c>
+    </row>
+    <row r="4591">
+      <c r="A4591" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C4591" t="n">
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>
@@ -37706,7 +37717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4590"/>
+  <dimension ref="A1:D4591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74719,6 +74730,12 @@
       <c r="A4589" s="4" t="n">
         <v>46304</v>
       </c>
+      <c r="B4589" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="C4589" t="n">
+        <v>10.1062</v>
+      </c>
       <c r="D4589" t="n">
         <v>12.5</v>
       </c>
@@ -74729,6 +74746,14 @@
       </c>
       <c r="D4590" t="n">
         <v>12.5</v>
+      </c>
+    </row>
+    <row r="4591">
+      <c r="A4591" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="D4591" t="n">
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4591</f>
+              <f>'Chart'!$D$2:$D$4592</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4591</f>
+              <f>'Chart'!$B$2:$B$4592</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4591</f>
+              <f>'Chart'!$D$2:$D$4592</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4591</f>
+              <f>'Chart'!$C$2:$C$4592</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 11 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 12 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4591"/>
+  <dimension ref="A1:D4592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37693,6 +37693,9 @@
       <c r="A4590" s="3" t="n">
         <v>46305</v>
       </c>
+      <c r="B4590" t="n">
+        <v>9.5525</v>
+      </c>
       <c r="C4590" t="n">
         <v>12.5</v>
       </c>
@@ -37703,6 +37706,14 @@
       </c>
       <c r="C4591" t="n">
         <v>11.5</v>
+      </c>
+    </row>
+    <row r="4592">
+      <c r="A4592" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C4592" t="n">
+        <v>11.36</v>
       </c>
     </row>
   </sheetData>
@@ -37717,7 +37728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4591"/>
+  <dimension ref="A1:D4592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74744,6 +74755,12 @@
       <c r="A4590" s="4" t="n">
         <v>46305</v>
       </c>
+      <c r="B4590" t="n">
+        <v>9.5525</v>
+      </c>
+      <c r="C4590" t="n">
+        <v>9.568199999999999</v>
+      </c>
       <c r="D4590" t="n">
         <v>12.5</v>
       </c>
@@ -74754,6 +74771,14 @@
       </c>
       <c r="D4591" t="n">
         <v>11.5</v>
+      </c>
+    </row>
+    <row r="4592">
+      <c r="A4592" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D4592" t="n">
+        <v>11.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4592</f>
+              <f>'Chart'!$D$2:$D$4609</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4592</f>
+              <f>'Chart'!$B$2:$B$4609</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4592</f>
+              <f>'Chart'!$D$2:$D$4609</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4592</f>
+              <f>'Chart'!$C$2:$C$4609</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 12 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 29 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4592"/>
+  <dimension ref="A1:D4609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37714,6 +37714,184 @@
       </c>
       <c r="C4592" t="n">
         <v>11.36</v>
+      </c>
+    </row>
+    <row r="4593">
+      <c r="A4593" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C4593" t="n">
+        <v>11.36</v>
+      </c>
+    </row>
+    <row r="4594">
+      <c r="A4594" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4594" t="n">
+        <v>11.4989</v>
+      </c>
+      <c r="C4594" t="n">
+        <v>11.36</v>
+      </c>
+    </row>
+    <row r="4595">
+      <c r="A4595" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4595" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4595" t="n">
+        <v>12.45</v>
+      </c>
+    </row>
+    <row r="4596">
+      <c r="A4596" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4596" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="C4596" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="4597">
+      <c r="A4597" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B4597" t="n">
+        <v>10.031</v>
+      </c>
+      <c r="C4597" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="4598">
+      <c r="A4598" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B4598" t="n">
+        <v>10.1444</v>
+      </c>
+      <c r="C4598" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="4599">
+      <c r="A4599" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4599" t="n">
+        <v>10.0005</v>
+      </c>
+      <c r="C4599" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="4600">
+      <c r="A4600" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4600" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="C4600" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4601">
+      <c r="A4601" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4601" t="n">
+        <v>11.1265</v>
+      </c>
+      <c r="C4601" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4602">
+      <c r="A4602" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4602" t="n">
+        <v>10.8655</v>
+      </c>
+      <c r="C4602" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4603">
+      <c r="A4603" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4603" t="n">
+        <v>11.0089</v>
+      </c>
+      <c r="C4603" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4604">
+      <c r="A4604" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B4604" t="n">
+        <v>10.8011</v>
+      </c>
+      <c r="C4604" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4605">
+      <c r="A4605" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B4605" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="C4605" t="n">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="4606">
+      <c r="A4606" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4606" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C4606" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4607">
+      <c r="A4607" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4607" t="n">
+        <v>11.2525</v>
+      </c>
+      <c r="C4607" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4608">
+      <c r="A4608" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C4608" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4609">
+      <c r="A4609" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C4609" t="n">
+        <v>12.28</v>
       </c>
     </row>
   </sheetData>
@@ -37728,7 +37906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4592"/>
+  <dimension ref="A1:D4609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74781,6 +74959,226 @@
         <v>11.36</v>
       </c>
     </row>
+    <row r="4593">
+      <c r="A4593" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="D4593" t="n">
+        <v>11.36</v>
+      </c>
+    </row>
+    <row r="4594">
+      <c r="A4594" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4594" t="n">
+        <v>11.4989</v>
+      </c>
+      <c r="C4594" t="n">
+        <v>11.4647</v>
+      </c>
+      <c r="D4594" t="n">
+        <v>11.36</v>
+      </c>
+    </row>
+    <row r="4595">
+      <c r="A4595" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4595" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4595" t="n">
+        <v>11.0494</v>
+      </c>
+      <c r="D4595" t="n">
+        <v>12.45</v>
+      </c>
+    </row>
+    <row r="4596">
+      <c r="A4596" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4596" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="C4596" t="n">
+        <v>10.8882</v>
+      </c>
+      <c r="D4596" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="4597">
+      <c r="A4597" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B4597" t="n">
+        <v>10.031</v>
+      </c>
+      <c r="C4597" t="n">
+        <v>10.0472</v>
+      </c>
+      <c r="D4597" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="4598">
+      <c r="A4598" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B4598" t="n">
+        <v>10.1444</v>
+      </c>
+      <c r="C4598" t="n">
+        <v>10.1606</v>
+      </c>
+      <c r="D4598" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="4599">
+      <c r="A4599" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4599" t="n">
+        <v>10.0005</v>
+      </c>
+      <c r="C4599" t="n">
+        <v>10.1758</v>
+      </c>
+      <c r="D4599" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="4600">
+      <c r="A4600" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4600" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="C4600" t="n">
+        <v>10.5132</v>
+      </c>
+      <c r="D4600" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4601">
+      <c r="A4601" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4601" t="n">
+        <v>11.1265</v>
+      </c>
+      <c r="C4601" t="n">
+        <v>11.1232</v>
+      </c>
+      <c r="D4601" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4602">
+      <c r="A4602" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4602" t="n">
+        <v>10.8655</v>
+      </c>
+      <c r="C4602" t="n">
+        <v>10.8771</v>
+      </c>
+      <c r="D4602" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4603">
+      <c r="A4603" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4603" t="n">
+        <v>11.0089</v>
+      </c>
+      <c r="C4603" t="n">
+        <v>11.0214</v>
+      </c>
+      <c r="D4603" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4604">
+      <c r="A4604" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B4604" t="n">
+        <v>10.8011</v>
+      </c>
+      <c r="C4604" t="n">
+        <v>10.8019</v>
+      </c>
+      <c r="D4604" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="4605">
+      <c r="A4605" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B4605" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="C4605" t="n">
+        <v>11.1364</v>
+      </c>
+      <c r="D4605" t="n">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="4606">
+      <c r="A4606" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4606" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C4606" t="n">
+        <v>11.4862</v>
+      </c>
+      <c r="D4606" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4607">
+      <c r="A4607" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4607" t="n">
+        <v>11.2525</v>
+      </c>
+      <c r="C4607" t="n">
+        <v>11.2518</v>
+      </c>
+      <c r="D4607" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4608">
+      <c r="A4608" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="D4608" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4609">
+      <c r="A4609" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="D4609" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4609</f>
+              <f>'Chart'!$D$2:$D$4610</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4609</f>
+              <f>'Chart'!$B$2:$B$4610</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4609</f>
+              <f>'Chart'!$D$2:$D$4610</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4609</f>
+              <f>'Chart'!$C$2:$C$4610</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 29 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 30 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4609"/>
+  <dimension ref="A1:D4610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37882,6 +37882,9 @@
       <c r="A4608" s="3" t="n">
         <v>46323</v>
       </c>
+      <c r="B4608" t="n">
+        <v>11.5</v>
+      </c>
       <c r="C4608" t="n">
         <v>12.28</v>
       </c>
@@ -37891,6 +37894,14 @@
         <v>46324</v>
       </c>
       <c r="C4609" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4610">
+      <c r="A4610" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C4610" t="n">
         <v>12.28</v>
       </c>
     </row>
@@ -37906,7 +37917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4609"/>
+  <dimension ref="A1:D4610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75167,6 +75178,12 @@
       <c r="A4608" s="4" t="n">
         <v>46323</v>
       </c>
+      <c r="B4608" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C4608" t="n">
+        <v>11.5074</v>
+      </c>
       <c r="D4608" t="n">
         <v>12.28</v>
       </c>
@@ -75176,6 +75193,14 @@
         <v>46324</v>
       </c>
       <c r="D4609" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4610">
+      <c r="A4610" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D4610" t="n">
         <v>12.28</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4610</f>
+              <f>'Chart'!$D$2:$D$4611</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4610</f>
+              <f>'Chart'!$B$2:$B$4611</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4610</f>
+              <f>'Chart'!$D$2:$D$4611</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4610</f>
+              <f>'Chart'!$C$2:$C$4611</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 30 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 31 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4610"/>
+  <dimension ref="A1:D4611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37893,6 +37893,9 @@
       <c r="A4609" s="3" t="n">
         <v>46324</v>
       </c>
+      <c r="B4609" t="n">
+        <v>11.3089</v>
+      </c>
       <c r="C4609" t="n">
         <v>12.28</v>
       </c>
@@ -37902,6 +37905,14 @@
         <v>46325</v>
       </c>
       <c r="C4610" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4611">
+      <c r="A4611" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="C4611" t="n">
         <v>12.28</v>
       </c>
     </row>
@@ -37917,7 +37928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4610"/>
+  <dimension ref="A1:D4611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75192,6 +75203,12 @@
       <c r="A4609" s="4" t="n">
         <v>46324</v>
       </c>
+      <c r="B4609" t="n">
+        <v>11.3089</v>
+      </c>
+      <c r="C4609" t="n">
+        <v>11.308</v>
+      </c>
       <c r="D4609" t="n">
         <v>12.28</v>
       </c>
@@ -75201,6 +75218,14 @@
         <v>46325</v>
       </c>
       <c r="D4610" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4611">
+      <c r="A4611" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="D4611" t="n">
         <v>12.28</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_hub_prices.xlsx
@@ -156,7 +156,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Australia gas hub prices: Victoria DWGM and Wallumbilla (AEMO) (to Oct/26)</a:t>
+              <a:t>Australia gas hub prices: Victoria DWGM and Wallumbilla (AEMO) (to Nov/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4611</f>
+              <f>'Chart'!$D$2:$D$4612</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4611</f>
+              <f>'Chart'!$B$2:$B$4612</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$D$2:$D$4611</f>
+              <f>'Chart'!$D$2:$D$4612</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4611</f>
+              <f>'Chart'!$C$2:$C$4612</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily, 19 Mar 2014 to 31 Oct 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
+          <t>Daily, 19 Mar 2014 to 01 Nov 2026. AEMO's current reports are rolling windows, so history builds from the archive read on the first run plus each daily run.</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4611"/>
+  <dimension ref="A1:D4612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37904,6 +37904,9 @@
       <c r="A4610" s="3" t="n">
         <v>46325</v>
       </c>
+      <c r="B4610" t="n">
+        <v>10.98</v>
+      </c>
       <c r="C4610" t="n">
         <v>12.28</v>
       </c>
@@ -37913,6 +37916,14 @@
         <v>46326</v>
       </c>
       <c r="C4611" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4612">
+      <c r="A4612" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C4612" t="n">
         <v>12.28</v>
       </c>
     </row>
@@ -37928,7 +37939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4611"/>
+  <dimension ref="A1:D4612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75217,6 +75228,12 @@
       <c r="A4610" s="4" t="n">
         <v>46325</v>
       </c>
+      <c r="B4610" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="C4610" t="n">
+        <v>10.9922</v>
+      </c>
       <c r="D4610" t="n">
         <v>12.28</v>
       </c>
@@ -75226,6 +75243,14 @@
         <v>46326</v>
       </c>
       <c r="D4611" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="4612">
+      <c r="A4612" s="4" t="n">
+        <v>46327</v>
+      </c>
+      <c r="D4612" t="n">
         <v>12.28</v>
       </c>
     </row>
